--- a/excel-audit-ae-as/Grille_evaluation_AE_AS_automatisee.xlsx
+++ b/excel-audit-ae-as/Grille_evaluation_AE_AS_automatisee.xlsx
@@ -3956,7 +3956,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="2" s="58"/>
+    <row r="3" s="58">
       <c r="A3" s="202" t="inlineStr">
         <is>
           <t>Année</t>
@@ -3971,7 +3972,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="58">
       <c r="A4" s="202" t="inlineStr">
         <is>
           <t>Agent suivi</t>
@@ -3984,6 +3985,7 @@
       </c>
       <c r="C4" s="204" t="n"/>
     </row>
+    <row r="5" s="58"/>
     <row r="6" ht="30" customHeight="1" s="58">
       <c r="A6" s="177" t="inlineStr">
         <is>
@@ -5895,6 +5897,7 @@
     <col width="9" customWidth="1" style="58" min="20" max="20"/>
   </cols>
   <sheetData>
+    <row r="1" s="58"/>
     <row r="2" ht="30" customHeight="1" s="58">
       <c r="A2" s="127" t="inlineStr">
         <is>
@@ -5902,14 +5905,15 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="58">
       <c r="A3" s="128" t="inlineStr">
         <is>
           <t>Saisissez un nom d'agent OU un log HERMES : tous les indicateurs et graphiques ci-dessous se recalculent automatiquement. Le log est prioritaire sur le nom s'il est renseigné.</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="4" s="58"/>
+    <row r="5" s="58">
       <c r="A5" s="129" t="inlineStr">
         <is>
           <t>Nom de l'agent</t>
@@ -5937,6 +5941,7 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="7" s="58"/>
     <row r="8" ht="26" customHeight="1" s="58">
       <c r="A8" s="132" t="inlineStr">
         <is>
@@ -8393,7 +8398,7 @@
       <c r="BM2" s="152" t="n"/>
       <c r="BN2" s="152" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" s="58">
       <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Nom de l'Agent :</t>
@@ -8480,7 +8485,7 @@
       <c r="BM3" s="27" t="n"/>
       <c r="BN3" s="27" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" s="58">
       <c r="A4" s="26" t="inlineStr">
         <is>
           <t>1. Choix de la Grille</t>
@@ -8737,7 +8742,7 @@
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="58">
       <c r="A5" s="26" t="inlineStr">
         <is>
           <t>2. Système de Notation</t>
@@ -8824,7 +8829,7 @@
       <c r="BM5" s="29" t="n"/>
       <c r="BN5" s="29" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" s="58">
       <c r="A6" s="26" t="inlineStr">
         <is>
           <t>3. Règle de Neutralisation</t>
@@ -8911,7 +8916,7 @@
       <c r="BM6" s="27" t="n"/>
       <c r="BN6" s="27" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" s="58">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>4. Pondération des Notes</t>
@@ -8998,7 +9003,7 @@
       <c r="BM7" s="27" t="n"/>
       <c r="BN7" s="27" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="58">
       <c r="A8" s="26" t="inlineStr">
         <is>
           <t>5. Plan d'Action</t>
@@ -9095,7 +9100,7 @@
       <c r="BM8" s="27" t="n"/>
       <c r="BN8" s="27" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" s="58">
       <c r="F9" s="35" t="inlineStr">
         <is>
           <t>Typologie de l'appel :</t>
@@ -9182,7 +9187,7 @@
       <c r="BM9" s="27" t="n"/>
       <c r="BN9" s="27" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="58">
       <c r="F10" s="34" t="inlineStr">
         <is>
           <t>Objet de l'appel :</t>
@@ -9269,7 +9274,7 @@
       <c r="BM10" s="27" t="n"/>
       <c r="BN10" s="27" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" s="58">
       <c r="F11" s="35" t="inlineStr">
         <is>
           <t>Autre à saisir :</t>
@@ -13605,7 +13610,7 @@
       <c r="BM2" s="168" t="n"/>
       <c r="BN2" s="168" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" s="58">
       <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Nom de l'Agent :</t>
@@ -13676,7 +13681,7 @@
       <c r="BM3" s="27" t="n"/>
       <c r="BN3" s="27" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" s="58">
       <c r="A4" s="26" t="inlineStr">
         <is>
           <t>1. Choix de la Grille</t>
@@ -13933,7 +13938,7 @@
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" s="58">
       <c r="A5" s="26" t="inlineStr">
         <is>
           <t>2. Système de Notation</t>
@@ -14012,7 +14017,7 @@
       <c r="BM5" s="29" t="n"/>
       <c r="BN5" s="29" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" s="58">
       <c r="A6" s="26" t="inlineStr">
         <is>
           <t>3. Règle de Neutralisation</t>
@@ -14091,7 +14096,7 @@
       <c r="BM6" s="27" t="n"/>
       <c r="BN6" s="27" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" s="58">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>4. Pondération des Notes</t>
@@ -14170,7 +14175,7 @@
       <c r="BM7" s="27" t="n"/>
       <c r="BN7" s="27" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="58">
       <c r="A8" s="26" t="inlineStr">
         <is>
           <t>5. Plan d'Action</t>
@@ -14251,7 +14256,7 @@
       <c r="BM8" s="27" t="n"/>
       <c r="BN8" s="27" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" s="58">
       <c r="F9" s="35" t="inlineStr">
         <is>
           <t>Typologie de l'appel :</t>
@@ -14322,7 +14327,7 @@
       <c r="BM9" s="31" t="n"/>
       <c r="BN9" s="31" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="58">
       <c r="F10" s="34" t="inlineStr">
         <is>
           <t>Objet de l'appel :</t>
@@ -14393,7 +14398,7 @@
       <c r="BM10" s="31" t="n"/>
       <c r="BN10" s="31" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" s="58">
       <c r="F11" s="35" t="inlineStr">
         <is>
           <t>Autre à saisir :</t>
@@ -28112,6 +28117,7 @@
     <col width="7" customWidth="1" style="58" min="20" max="20"/>
   </cols>
   <sheetData>
+    <row r="1" s="58"/>
     <row r="2" ht="30" customHeight="1" s="58">
       <c r="A2" s="127" t="inlineStr">
         <is>
@@ -28119,14 +28125,14 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="58">
       <c r="A3" s="128" t="inlineStr">
         <is>
           <t>AL BARID BANK — Centre de Relations Clients · Pondération 70 % Fond / 30 % Forme · toutes les valeurs sont calculées depuis l'onglet « Historique AE AS »</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="58">
       <c r="A4" s="129" t="inlineStr">
         <is>
           <t>Année</t>
@@ -28185,6 +28191,7 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="6" s="58"/>
     <row r="7" ht="16" customHeight="1" s="58">
       <c r="A7" s="137" t="inlineStr">
         <is>
@@ -28239,7 +28246,7 @@
       <c r="S7" s="138" t="n"/>
       <c r="T7" s="138" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" s="58">
       <c r="A8" s="186">
         <f>COUNTIFS('Historique AE AS'!$L$4:$L$123,$A$5,'Historique AE AS'!$K$4:$K$123,"&gt;="&amp;$C$5,'Historique AE AS'!$K$4:$K$123,"&lt;="&amp;$D$5,'Historique AE AS'!$D$4:$D$123,IF($B$5="Tous","*",$B$5))</f>
         <v/>
@@ -28307,6 +28314,7 @@
       <c r="S9" s="138" t="n"/>
       <c r="T9" s="138" t="n"/>
     </row>
+    <row r="10" s="58"/>
     <row r="11" ht="38" customHeight="1" s="58">
       <c r="A11" s="177" t="inlineStr">
         <is>
@@ -32849,6 +32857,7 @@
     <col width="18" customWidth="1" style="58" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1" s="58"/>
     <row r="2" ht="30" customHeight="1" s="58">
       <c r="A2" s="127" t="inlineStr">
         <is>
@@ -32856,13 +32865,14 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" s="58">
       <c r="A3" s="128" t="inlineStr">
         <is>
           <t>Moyenne de chaque critère sur l'ensemble des évaluations saisies dans la grille correspondante (colonnes G à BN). Les critères notés « N/A » sont neutralisés.</t>
         </is>
       </c>
     </row>
+    <row r="4" s="58"/>
     <row r="5" ht="30" customHeight="1" s="58">
       <c r="A5" s="177" t="inlineStr">
         <is>
